--- a/public/templates/worker-roster.xlsx
+++ b/public/templates/worker-roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanse\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19E3D58B-7D64-44A8-85B1-2FDE26B05D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6EBB7E-C950-421B-8C67-E29FE8BC5BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C806C3F8-CC2E-4162-A21B-7B41819F853A}"/>
+    <workbookView xWindow="5595" yWindow="1860" windowWidth="22995" windowHeight="13695" xr2:uid="{C806C3F8-CC2E-4162-A21B-7B41819F853A}"/>
   </bookViews>
   <sheets>
     <sheet name="作業員名簿" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="55">
   <si>
     <t>全建統一様式第２号</t>
     <rPh sb="0" eb="2">
@@ -635,12 +635,32 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>雇用年月日</t>
+    <rPh sb="0" eb="5">
+      <t>コヨウネンガッピ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>雇入・職長
+特別教育</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>技能講習</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>免許</t>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -696,6 +716,27 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1026,8 +1067,261 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1037,274 +1331,189 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1343,7 +1552,7 @@
         <xdr:cNvPr id="2" name="Oval 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{805B23FC-4C17-4556-A01E-B94FE0FED7B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1409,7 +1618,7 @@
         <xdr:cNvPr id="3" name="Oval 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE56844-BE93-4FA3-86C1-0FC29A2F6EC3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1475,7 +1684,7 @@
         <xdr:cNvPr id="4" name="Oval 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3447DFD2-4F78-446B-BCFA-F517951C4790}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1541,7 +1750,7 @@
         <xdr:cNvPr id="5" name="Oval 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7060C566-A9C7-4DA0-BC53-7242E9EBAC07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1607,7 +1816,7 @@
         <xdr:cNvPr id="6" name="Oval 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3EAE3F7-4CAB-46AD-B20C-7C2597D56781}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1673,7 +1882,7 @@
         <xdr:cNvPr id="7" name="Oval 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C679AFE8-327E-4B87-9D1E-E45911F392DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1739,7 +1948,7 @@
         <xdr:cNvPr id="8" name="Oval 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F0C280-B592-4287-A29C-6C4599B3D9A5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1805,7 +2014,7 @@
         <xdr:cNvPr id="9" name="Group 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E18BC1D2-FD45-41F2-94A5-C92CB843DBB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1826,7 +2035,7 @@
           <xdr:cNvPr id="10" name="Text Box 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{290FAFB9-2E5C-4F6E-B201-7803E58F912A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1866,7 +2075,7 @@
           <xdr:cNvPr id="11" name="Text Box 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E51682D-73AE-45FE-BBC0-18933C78BAFD}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1939,7 +2148,7 @@
           <xdr:cNvPr id="12" name="Text Box 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1614FC8B-9D33-4D6C-8CFF-BD0763125F44}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1985,7 +2194,7 @@
           <xdr:cNvPr id="13" name="Text Box 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{895FC955-7251-409B-94C1-C61D2DECBE65}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2036,7 +2245,7 @@
                     <a14:compatExt spid="_x0000_s1025"/>
                   </a:ext>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F694722-D218-49AF-8AFD-2BD3823D9976}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -2054,7 +2263,6 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
               <a:extLst>
                 <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
                   <a14:hiddenFill>
@@ -2073,15 +2281,6 @@
                     <a:tailEnd/>
                   </a14:hiddenLine>
                 </a:ext>
-                <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                  <a14:hiddenEffects>
-                    <a:effectLst>
-                      <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                        <a:srgbClr val="808080"/>
-                      </a:outerShdw>
-                    </a:effectLst>
-                  </a14:hiddenEffects>
-                </a:ext>
               </a:extLst>
             </xdr:spPr>
           </xdr:sp>
@@ -2098,7 +2297,7 @@
                     <a14:compatExt spid="_x0000_s1026"/>
                   </a:ext>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC2975A-A5A0-4BB4-839D-15452550CAB4}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -2116,7 +2315,6 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
               <a:extLst>
                 <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
                   <a14:hiddenFill>
@@ -2135,15 +2333,6 @@
                     <a:tailEnd/>
                   </a14:hiddenLine>
                 </a:ext>
-                <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                  <a14:hiddenEffects>
-                    <a:effectLst>
-                      <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                        <a:srgbClr val="808080"/>
-                      </a:outerShdw>
-                    </a:effectLst>
-                  </a14:hiddenEffects>
-                </a:ext>
               </a:extLst>
             </xdr:spPr>
           </xdr:sp>
@@ -2157,9 +2346,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2197,7 +2386,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2303,7 +2492,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2445,7 +2634,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3483,1649 +3672,1804 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" spans="2:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="91"/>
+      <c r="S2" s="91"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
     </row>
     <row r="3" spans="2:22" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
     </row>
     <row r="4" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="74"/>
+      <c r="D4" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="11" t="s">
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
+      <c r="U4" s="96"/>
+      <c r="V4" s="96"/>
     </row>
     <row r="5" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="74"/>
+      <c r="D5" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="4" t="s">
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="15" t="s">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="16"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="18" t="s">
+      <c r="O5" s="79"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="18" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
     </row>
     <row r="7" spans="2:22" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
     </row>
     <row r="8" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25" t="s">
+      <c r="D8" s="42"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="25" t="s">
+      <c r="I8" s="86"/>
+      <c r="J8" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="31" t="s">
+      <c r="L8" s="26"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="33" t="s">
+      <c r="O8" s="66"/>
+      <c r="P8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="21" t="s">
+      <c r="Q8" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="33" t="s">
+      <c r="R8" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="S8" s="34" t="s">
+      <c r="S8" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="T8" s="35"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="37" t="s">
+      <c r="T8" s="57"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:22" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="38"/>
-      <c r="C9" s="39" t="s">
+      <c r="B9" s="83"/>
+      <c r="C9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="53"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="46"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="142"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="59"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="62"/>
     </row>
     <row r="10" spans="2:22" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="55"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="61" t="s">
+      <c r="B10" s="84"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="63" t="s">
+      <c r="I10" s="20"/>
+      <c r="J10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="64" t="s">
+      <c r="K10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="66" t="s">
+      <c r="L10" s="22"/>
+      <c r="M10" s="143"/>
+      <c r="N10" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="67"/>
-      <c r="P10" s="63" t="s">
+      <c r="O10" s="64"/>
+      <c r="P10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="63" t="s">
+      <c r="Q10" s="73"/>
+      <c r="R10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="S10" s="69" t="s">
+      <c r="S10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T10" s="63" t="s">
+      <c r="T10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="U10" s="63" t="s">
+      <c r="U10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V10" s="70" t="s">
+      <c r="V10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="71"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="72" t="s">
+      <c r="B11" s="97">
+        <v>1</v>
+      </c>
+      <c r="C11" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="99"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="101" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="102"/>
+      <c r="H11" s="103" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="104"/>
+      <c r="J11" s="105" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="107"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="147" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" s="148"/>
+      <c r="P11" s="108" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="R11" s="108" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="T11" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="U11" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="V11" s="111" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="112"/>
+      <c r="C12" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="114"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="149"/>
+      <c r="O12" s="150"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="124"/>
+      <c r="R12" s="123"/>
+      <c r="S12" s="125"/>
+      <c r="T12" s="125"/>
+      <c r="U12" s="125"/>
+      <c r="V12" s="126"/>
+    </row>
+    <row r="13" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="127"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="133" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="134"/>
+      <c r="J13" s="135" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="137"/>
+      <c r="M13" s="146"/>
+      <c r="N13" s="151" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" s="152"/>
+      <c r="P13" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="138"/>
+      <c r="R13" s="135" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" s="139"/>
+      <c r="T13" s="139"/>
+      <c r="U13" s="139"/>
+      <c r="V13" s="140" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="33"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="73"/>
-      <c r="J11" s="74" t="s">
+      <c r="I14" s="51"/>
+      <c r="J14" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="29"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="77" t="s">
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="141"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="77" t="s">
+      <c r="Q14" s="33"/>
+      <c r="R14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S11" s="78"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="77" t="s">
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="79"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="85"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="87"/>
-      <c r="U12" s="87"/>
-      <c r="V12" s="85"/>
-    </row>
-    <row r="13" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="88"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="61" t="s">
+    <row r="15" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="39"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="142"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="37"/>
+      <c r="T15" s="37"/>
+      <c r="U15" s="37"/>
+      <c r="V15" s="11"/>
+    </row>
+    <row r="16" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="40"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="62"/>
-      <c r="J13" s="63" t="s">
+      <c r="I16" s="20"/>
+      <c r="J16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="64"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="63" t="s">
+      <c r="K16" s="21"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="92"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="92"/>
-      <c r="V13" s="93" t="s">
+      <c r="Q16" s="35"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="71"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="72" t="s">
+    <row r="17" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="33"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="73"/>
-      <c r="J14" s="74" t="s">
+      <c r="I17" s="51"/>
+      <c r="J17" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="29"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="76"/>
-      <c r="P14" s="77" t="s">
+      <c r="K17" s="25"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="77" t="s">
+      <c r="Q17" s="33"/>
+      <c r="R17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="77" t="s">
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="79"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="86"/>
-      <c r="R15" s="85"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="87"/>
-      <c r="U15" s="87"/>
-      <c r="V15" s="85"/>
-    </row>
-    <row r="16" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="88"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="61" t="s">
+    <row r="18" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="39"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="142"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="37"/>
+      <c r="T18" s="37"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="11"/>
+    </row>
+    <row r="19" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="40"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="63" t="s">
+      <c r="I19" s="20"/>
+      <c r="J19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="64"/>
-      <c r="L16" s="65"/>
-      <c r="M16" s="65"/>
-      <c r="N16" s="89"/>
-      <c r="O16" s="90"/>
-      <c r="P16" s="63" t="s">
+      <c r="K19" s="21"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="143"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="63"/>
-      <c r="S16" s="92"/>
-      <c r="T16" s="92"/>
-      <c r="U16" s="92"/>
-      <c r="V16" s="93" t="s">
+      <c r="Q19" s="35"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="71"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="72" t="s">
+    <row r="20" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="33"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="73"/>
-      <c r="J17" s="74" t="s">
+      <c r="I20" s="51"/>
+      <c r="J20" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K17" s="29"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="75"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="77" t="s">
+      <c r="K20" s="25"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="77" t="s">
+      <c r="Q20" s="33"/>
+      <c r="R20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S17" s="78"/>
-      <c r="T17" s="78"/>
-      <c r="U17" s="78"/>
-      <c r="V17" s="77" t="s">
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="79"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="83"/>
-      <c r="O18" s="84"/>
-      <c r="P18" s="85"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="85"/>
-      <c r="S18" s="87"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="87"/>
-      <c r="V18" s="85"/>
-    </row>
-    <row r="19" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="88"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="61" t="s">
+    <row r="21" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="39"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="142"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="11"/>
+    </row>
+    <row r="22" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="40"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="62"/>
-      <c r="J19" s="63" t="s">
+      <c r="I22" s="20"/>
+      <c r="J22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="64"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="89"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="63" t="s">
+      <c r="K22" s="21"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="143"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q19" s="91"/>
-      <c r="R19" s="63"/>
-      <c r="S19" s="92"/>
-      <c r="T19" s="92"/>
-      <c r="U19" s="92"/>
-      <c r="V19" s="93" t="s">
+      <c r="Q22" s="35"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="71"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="72" t="s">
+    <row r="23" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="33"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I20" s="73"/>
-      <c r="J20" s="74" t="s">
+      <c r="I23" s="51"/>
+      <c r="J23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="29"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="75"/>
-      <c r="O20" s="76"/>
-      <c r="P20" s="77" t="s">
+      <c r="K23" s="25"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="141"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="77" t="s">
+      <c r="Q23" s="33"/>
+      <c r="R23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S20" s="78"/>
-      <c r="T20" s="78"/>
-      <c r="U20" s="78"/>
-      <c r="V20" s="77" t="s">
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="79"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="84"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="86"/>
-      <c r="R21" s="85"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="87"/>
-      <c r="U21" s="87"/>
-      <c r="V21" s="85"/>
-    </row>
-    <row r="22" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="88"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="61" t="s">
+    <row r="24" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="39"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="142"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="11"/>
+    </row>
+    <row r="25" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="40"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="63" t="s">
+      <c r="I25" s="20"/>
+      <c r="J25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="64"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="63" t="s">
+      <c r="K25" s="21"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="143"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q22" s="91"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="92"/>
-      <c r="T22" s="92"/>
-      <c r="U22" s="92"/>
-      <c r="V22" s="93" t="s">
+      <c r="Q25" s="35"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="71"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="72" t="s">
+    <row r="26" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="33"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="73"/>
-      <c r="J23" s="74" t="s">
+      <c r="I26" s="51"/>
+      <c r="J26" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K23" s="29"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="75"/>
-      <c r="O23" s="76"/>
-      <c r="P23" s="77" t="s">
+      <c r="K26" s="25"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="77" t="s">
+      <c r="Q26" s="33"/>
+      <c r="R26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="77" t="s">
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="79"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="86"/>
-      <c r="R24" s="85"/>
-      <c r="S24" s="87"/>
-      <c r="T24" s="87"/>
-      <c r="U24" s="87"/>
-      <c r="V24" s="85"/>
-    </row>
-    <row r="25" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="88"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="61" t="s">
+    <row r="27" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="39"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="142"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="11"/>
+    </row>
+    <row r="28" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="40"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="62"/>
-      <c r="J25" s="63" t="s">
+      <c r="I28" s="20"/>
+      <c r="J28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="64"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
-      <c r="P25" s="63" t="s">
+      <c r="K28" s="21"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="143"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="63"/>
-      <c r="S25" s="92"/>
-      <c r="T25" s="92"/>
-      <c r="U25" s="92"/>
-      <c r="V25" s="93" t="s">
+      <c r="Q28" s="35"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="71"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="72" t="s">
+    <row r="29" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="33"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="73"/>
-      <c r="J26" s="74" t="s">
+      <c r="I29" s="51"/>
+      <c r="J29" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K26" s="29"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="76"/>
-      <c r="P26" s="77" t="s">
+      <c r="K29" s="25"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="77" t="s">
+      <c r="Q29" s="33"/>
+      <c r="R29" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S26" s="78"/>
-      <c r="T26" s="78"/>
-      <c r="U26" s="78"/>
-      <c r="V26" s="77" t="s">
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="79"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="82"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="86"/>
-      <c r="R27" s="85"/>
-      <c r="S27" s="87"/>
-      <c r="T27" s="87"/>
-      <c r="U27" s="87"/>
-      <c r="V27" s="85"/>
-    </row>
-    <row r="28" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="88"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="61" t="s">
+    <row r="30" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="39"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="142"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="11"/>
+    </row>
+    <row r="31" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="40"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="62"/>
-      <c r="J28" s="63" t="s">
+      <c r="I31" s="20"/>
+      <c r="J31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="64"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="63" t="s">
+      <c r="K31" s="21"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="63"/>
-      <c r="S28" s="92"/>
-      <c r="T28" s="92"/>
-      <c r="U28" s="92"/>
-      <c r="V28" s="93" t="s">
+      <c r="Q31" s="35"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="71"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="72" t="s">
+    <row r="32" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="33"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="73"/>
-      <c r="J29" s="74" t="s">
+      <c r="I32" s="51"/>
+      <c r="J32" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="29"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="75"/>
-      <c r="O29" s="76"/>
-      <c r="P29" s="77" t="s">
+      <c r="K32" s="25"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="77" t="s">
+      <c r="Q32" s="33"/>
+      <c r="R32" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S29" s="78"/>
-      <c r="T29" s="78"/>
-      <c r="U29" s="78"/>
-      <c r="V29" s="77" t="s">
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="36"/>
+      <c r="V32" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="79"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="82"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="86"/>
-      <c r="R30" s="85"/>
-      <c r="S30" s="87"/>
-      <c r="T30" s="87"/>
-      <c r="U30" s="87"/>
-      <c r="V30" s="85"/>
-    </row>
-    <row r="31" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="88"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="61" t="s">
+    <row r="33" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="39"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="142"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="37"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="11"/>
+    </row>
+    <row r="34" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="40"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="62"/>
-      <c r="J31" s="63" t="s">
+      <c r="I34" s="20"/>
+      <c r="J34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="64"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
-      <c r="P31" s="63" t="s">
+      <c r="K34" s="21"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="143"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q31" s="91"/>
-      <c r="R31" s="63"/>
-      <c r="S31" s="92"/>
-      <c r="T31" s="92"/>
-      <c r="U31" s="92"/>
-      <c r="V31" s="93" t="s">
+      <c r="Q34" s="35"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="71"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="72" t="s">
+    <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="33"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="73"/>
-      <c r="J32" s="74" t="s">
+      <c r="I35" s="51"/>
+      <c r="J35" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="29"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="77" t="s">
+      <c r="K35" s="25"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="141"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="77" t="s">
+      <c r="Q35" s="33"/>
+      <c r="R35" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S32" s="78"/>
-      <c r="T32" s="78"/>
-      <c r="U32" s="78"/>
-      <c r="V32" s="77" t="s">
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="36"/>
+      <c r="V35" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="79"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="84"/>
-      <c r="P33" s="85"/>
-      <c r="Q33" s="86"/>
-      <c r="R33" s="85"/>
-      <c r="S33" s="87"/>
-      <c r="T33" s="87"/>
-      <c r="U33" s="87"/>
-      <c r="V33" s="85"/>
-    </row>
-    <row r="34" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="88"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="61" t="s">
+    <row r="36" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="39"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="142"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="37"/>
+      <c r="T36" s="37"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="11"/>
+    </row>
+    <row r="37" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="40"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I34" s="62"/>
-      <c r="J34" s="63" t="s">
+      <c r="I37" s="20"/>
+      <c r="J37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K34" s="64"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="90"/>
-      <c r="P34" s="63" t="s">
+      <c r="K37" s="21"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="143"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="63"/>
-      <c r="S34" s="92"/>
-      <c r="T34" s="92"/>
-      <c r="U34" s="92"/>
-      <c r="V34" s="93" t="s">
+      <c r="Q37" s="35"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="71"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="72" t="s">
+    <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="33"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="73"/>
-      <c r="J35" s="74" t="s">
+      <c r="I38" s="51"/>
+      <c r="J38" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K35" s="29"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="77" t="s">
+      <c r="K38" s="25"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="141"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="77" t="s">
+      <c r="Q38" s="33"/>
+      <c r="R38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S35" s="78"/>
-      <c r="T35" s="78"/>
-      <c r="U35" s="78"/>
-      <c r="V35" s="77" t="s">
+      <c r="S38" s="36"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="79"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="82"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="48"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="84"/>
-      <c r="P36" s="85"/>
-      <c r="Q36" s="86"/>
-      <c r="R36" s="85"/>
-      <c r="S36" s="87"/>
-      <c r="T36" s="87"/>
-      <c r="U36" s="87"/>
-      <c r="V36" s="85"/>
-    </row>
-    <row r="37" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="88"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="61" t="s">
+    <row r="39" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="12"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="142"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="37"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
+      <c r="V39" s="11"/>
+    </row>
+    <row r="40" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="12"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I37" s="62"/>
-      <c r="J37" s="63" t="s">
+      <c r="I40" s="20"/>
+      <c r="J40" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K37" s="64"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="89"/>
-      <c r="O37" s="90"/>
-      <c r="P37" s="63" t="s">
+      <c r="K40" s="21"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q37" s="91"/>
-      <c r="R37" s="63"/>
-      <c r="S37" s="92"/>
-      <c r="T37" s="92"/>
-      <c r="U37" s="92"/>
-      <c r="V37" s="93" t="s">
+      <c r="Q40" s="35"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="71"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="I38" s="73"/>
-      <c r="J38" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="K38" s="29"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="S38" s="78"/>
-      <c r="T38" s="37"/>
-      <c r="U38" s="37"/>
-      <c r="V38" s="77" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="94"/>
-      <c r="B39" s="79"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="48"/>
-      <c r="M39" s="48"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="84"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="86"/>
-      <c r="R39" s="85"/>
-      <c r="S39" s="87"/>
-      <c r="T39" s="95"/>
-      <c r="U39" s="95"/>
-      <c r="V39" s="85"/>
-    </row>
-    <row r="40" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="94"/>
-      <c r="B40" s="88"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="60"/>
-      <c r="H40" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="62"/>
-      <c r="J40" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="K40" s="64"/>
-      <c r="L40" s="65"/>
-      <c r="M40" s="65"/>
-      <c r="N40" s="89"/>
-      <c r="O40" s="90"/>
-      <c r="P40" s="63" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q40" s="91"/>
-      <c r="R40" s="63"/>
-      <c r="S40" s="92"/>
-      <c r="T40" s="96"/>
-      <c r="U40" s="96"/>
-      <c r="V40" s="93" t="s">
-        <v>39</v>
-      </c>
-    </row>
     <row r="41" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4" t="s">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4" t="s">
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4" t="s">
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4" t="s">
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4" t="s">
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4" t="s">
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4" t="s">
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4" t="s">
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
     </row>
     <row r="51" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
     </row>
     <row r="52" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
     </row>
     <row r="53" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
     </row>
     <row r="54" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
     </row>
     <row r="55" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
     </row>
     <row r="56" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.15">
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="219">
-    <mergeCell ref="T38:T40"/>
-    <mergeCell ref="U38:U40"/>
-    <mergeCell ref="V38:V39"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="C39:E40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="K38:M39"/>
-    <mergeCell ref="N38:O39"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="Q38:Q40"/>
-    <mergeCell ref="R38:R39"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="H38:I39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="T35:T37"/>
-    <mergeCell ref="U35:U37"/>
-    <mergeCell ref="V35:V36"/>
-    <mergeCell ref="C36:E37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="K35:M36"/>
-    <mergeCell ref="N35:O36"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:S37"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="B3:S3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:R6"/>
+    <mergeCell ref="T5:V6"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:I9"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="S8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="C9:E10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:M9"/>
+    <mergeCell ref="N8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="C12:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="K11:M12"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="T14:T16"/>
+    <mergeCell ref="U14:U16"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="C15:E16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="K14:M15"/>
+    <mergeCell ref="N14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="T17:T19"/>
+    <mergeCell ref="U17:U19"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="C18:E19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="N17:O18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="Q17:Q19"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="T20:T22"/>
+    <mergeCell ref="U20:U22"/>
+    <mergeCell ref="V20:V21"/>
+    <mergeCell ref="C21:E22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="K20:M21"/>
+    <mergeCell ref="N20:O21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="Q20:Q22"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="S20:S22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="H20:I21"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="T23:T25"/>
+    <mergeCell ref="U23:U25"/>
+    <mergeCell ref="V23:V24"/>
+    <mergeCell ref="C24:E25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="K23:M24"/>
+    <mergeCell ref="N23:O24"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="Q23:Q25"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="V26:V27"/>
+    <mergeCell ref="C27:E28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="N26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="Q26:Q28"/>
+    <mergeCell ref="R26:R27"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="H26:I27"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="T29:T31"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="V29:V30"/>
+    <mergeCell ref="C30:E31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="K29:M30"/>
+    <mergeCell ref="N29:O30"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="Q29:Q31"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S31"/>
     <mergeCell ref="B35:B37"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="F35:F37"/>
@@ -5150,168 +5494,39 @@
     <mergeCell ref="F32:F34"/>
     <mergeCell ref="G32:G34"/>
     <mergeCell ref="H32:I33"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="T29:T31"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="V29:V30"/>
-    <mergeCell ref="C30:E31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="K29:M30"/>
-    <mergeCell ref="N29:O30"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="Q29:Q31"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="V26:V27"/>
-    <mergeCell ref="C27:E28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="K26:M27"/>
-    <mergeCell ref="N26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="Q26:Q28"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="H26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="T23:T25"/>
-    <mergeCell ref="U23:U25"/>
-    <mergeCell ref="V23:V24"/>
-    <mergeCell ref="C24:E25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="K23:M24"/>
-    <mergeCell ref="N23:O24"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="Q23:Q25"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="T20:T22"/>
-    <mergeCell ref="U20:U22"/>
-    <mergeCell ref="V20:V21"/>
-    <mergeCell ref="C21:E22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="K20:M21"/>
-    <mergeCell ref="N20:O21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="Q20:Q22"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="S20:S22"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="H20:I21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="T17:T19"/>
-    <mergeCell ref="U17:U19"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="C18:E19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="N17:O18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="Q17:Q19"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="T14:T16"/>
-    <mergeCell ref="U14:U16"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="C15:E16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="K14:M15"/>
-    <mergeCell ref="N14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q16"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="C12:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="K11:M12"/>
-    <mergeCell ref="N11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="S8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="C9:E10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:M9"/>
-    <mergeCell ref="N8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:R6"/>
-    <mergeCell ref="T5:V6"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="H8:I9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:S2"/>
-    <mergeCell ref="B3:S3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="T35:T37"/>
+    <mergeCell ref="U35:U37"/>
+    <mergeCell ref="V35:V36"/>
+    <mergeCell ref="C36:E37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="K35:M36"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:S37"/>
+    <mergeCell ref="T38:T40"/>
+    <mergeCell ref="U38:U40"/>
+    <mergeCell ref="V38:V39"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="C39:E40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="K38:M39"/>
+    <mergeCell ref="N38:O39"/>
+    <mergeCell ref="P38:P39"/>
+    <mergeCell ref="Q38:Q40"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="H38:I39"/>
+    <mergeCell ref="J38:J39"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.39370078740157483" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
